--- a/docs/d/56/inyear.xlsx
+++ b/docs/d/56/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 63 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 60 clubs short</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1229,8 +1229,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -2001,17 +2001,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M13" s="7" t="n">
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="9" t="n">
         <v>0</v>
@@ -6093,13 +6093,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -12488,7 +12488,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12558,8 +12558,8 @@
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -14629,7 +14629,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14699,8 +14699,8 @@
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="9" t="n">
-        <v>0</v>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
@@ -15525,7 +15525,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -15606,7 +15606,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -16251,7 +16251,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16383,7 +16383,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>

--- a/docs/d/56/inyear.xlsx
+++ b/docs/d/56/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,11 @@
       <c r="AB6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1860,7 +1864,11 @@
       <c r="AB11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2272,7 +2280,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3084,7 +3096,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3286,7 +3302,11 @@
       <c r="AB25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -5653,7 +5673,11 @@
       <c r="AB48" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC48" s="4" t="inlineStr"/>
+      <c r="AC48" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -5754,7 +5778,11 @@
       <c r="AB49" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC49" s="4" t="inlineStr"/>
+      <c r="AC49" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -6057,7 +6085,11 @@
       <c r="AB52" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC52" s="4" t="inlineStr"/>
+      <c r="AC52" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6562,7 +6594,11 @@
       <c r="AB57" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC57" s="4" t="inlineStr"/>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -7075,7 +7111,11 @@
       <c r="AB62" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC62" s="4" t="inlineStr"/>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -8715,7 +8755,11 @@
       <c r="AB78" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC78" s="4" t="inlineStr"/>
+      <c r="AC78" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -9531,7 +9575,11 @@
       <c r="AB86" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC86" s="4" t="inlineStr"/>
+      <c r="AC86" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -9632,7 +9680,11 @@
       <c r="AB87" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC87" s="4" t="inlineStr"/>
+      <c r="AC87" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -9733,7 +9785,11 @@
       <c r="AB88" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC88" s="4" t="inlineStr"/>
+      <c r="AC88" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -9834,7 +9890,11 @@
       <c r="AB89" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -10242,7 +10302,11 @@
       <c r="AB93" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC93" s="4" t="inlineStr"/>
+      <c r="AC93" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -11347,7 +11411,11 @@
       <c r="AB104" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC104" s="4" t="inlineStr"/>
+      <c r="AC104" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -11957,7 +12025,11 @@
       <c r="AB110" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC110" s="4" t="inlineStr"/>
+      <c r="AC110" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -13484,7 +13556,11 @@
       <c r="AB125" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC125" s="4" t="inlineStr"/>
+      <c r="AC125" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -14199,7 +14275,11 @@
       <c r="AB132" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC132" s="4" t="inlineStr"/>
+      <c r="AC132" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -15124,7 +15204,11 @@
       <c r="AB141" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC141" s="4" t="inlineStr"/>
+      <c r="AC141" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">

--- a/docs/d/56/inyear.xlsx
+++ b/docs/d/56/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 60 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 54 clubs short</t>
         </is>
       </c>
     </row>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>1</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="9" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1544,8 +1544,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4316,8 +4316,8 @@
       <c r="T35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U35" s="9" t="n">
-        <v>0</v>
+      <c r="U35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V35" s="9" t="n">
         <v>1</v>
@@ -5493,7 +5493,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5563,8 +5563,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>0</v>
@@ -9651,7 +9651,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" s="10" t="n">
         <v>1</v>
@@ -11946,7 +11946,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11989,8 +11989,8 @@
       <c r="P110" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" s="9" t="n">
-        <v>1</v>
+      <c r="Q110" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
@@ -12051,7 +12051,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12121,8 +12121,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -12766,7 +12766,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12836,8 +12836,8 @@
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -13073,7 +13073,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13143,8 +13143,8 @@
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -13743,7 +13743,7 @@
         <v>1</v>
       </c>
       <c r="U127" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V127" s="9" t="n">
         <v>2</v>
@@ -14196,7 +14196,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14248,8 +14248,8 @@
       <c r="S132" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T132" s="9" t="n">
-        <v>0</v>
+      <c r="T132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U132" s="9" t="n">
         <v>0</v>
@@ -14919,7 +14919,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14989,8 +14989,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -15642,7 +15642,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15807,7 +15807,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15906,7 +15906,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -16302,7 +16302,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16335,7 +16335,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16368,7 +16368,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16434,7 +16434,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -16467,7 +16467,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>

--- a/docs/d/56/inyear.xlsx
+++ b/docs/d/56/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 54 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="P6" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="10" t="n">
         <v>2</v>
@@ -1754,8 +1754,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="9" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="P13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>0</v>
@@ -2065,8 +2065,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="P23" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="9" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3192,8 +3192,8 @@
       <c r="Y24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="9" t="n">
-        <v>0</v>
+      <c r="Z24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA24" s="10" t="n">
         <v>1</v>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3398,8 +3398,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3447,17 +3447,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M27" s="7" t="n">
@@ -3494,8 +3494,8 @@
       <c r="V27" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W27" s="9" t="n">
-        <v>0</v>
+      <c r="W27" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>6</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3709,8 +3709,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3814,8 +3814,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3919,8 +3919,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4125,8 +4125,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -4376,13 +4376,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4925,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" s="9" t="n">
         <v>0</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="P42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42" s="9" t="n">
         <v>1</v>
@@ -5081,7 +5081,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5136,8 +5136,8 @@
       <c r="T43" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U43" s="9" t="n">
-        <v>0</v>
+      <c r="U43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V43" s="10" t="n">
         <v>4</v>
@@ -5608,13 +5608,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>4</v>
       </c>
       <c r="W48" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6125,13 +6125,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6181,8 +6181,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -6620,7 +6620,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6690,8 +6690,8 @@
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7413,8 +7413,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7619,8 +7619,8 @@
       <c r="Y67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z67" s="9" t="n">
-        <v>0</v>
+      <c r="Z67" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA67" s="10" t="n">
         <v>1</v>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7825,8 +7825,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8136,8 +8136,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8544,8 +8544,8 @@
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="9" t="n">
-        <v>0</v>
+      <c r="Z76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -8717,7 +8717,7 @@
         </is>
       </c>
       <c r="P78" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q78" s="9" t="n">
         <v>0</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8851,8 +8851,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -8882,7 +8882,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8946,14 +8946,14 @@
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X80" s="9" t="n">
-        <v>3</v>
+      <c r="X80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -9253,8 +9253,8 @@
       <c r="W83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X83" s="9" t="n">
-        <v>3</v>
+      <c r="X83" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
@@ -9916,7 +9916,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9930,13 +9930,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L90" s="8" t="inlineStr">
         <is>
@@ -9974,8 +9974,8 @@
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="9" t="n">
-        <v>3</v>
+      <c r="V90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10705,8 +10705,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10934,7 +10934,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -11004,8 +11004,8 @@
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11301,8 +11301,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -12156,7 +12156,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12226,8 +12226,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12327,8 +12327,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
@@ -13275,7 +13275,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13345,8 +13345,8 @@
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="9" t="n">
-        <v>0</v>
+      <c r="Z123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA123" s="10" t="n">
         <v>1</v>
@@ -13518,10 +13518,10 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q126" s="9" t="n">
         <v>0</v>
@@ -13792,7 +13792,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13862,8 +13862,8 @@
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -13893,7 +13893,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13963,8 +13963,8 @@
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -14301,7 +14301,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14371,8 +14371,8 @@
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -14507,7 +14507,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14577,8 +14577,8 @@
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -15675,7 +15675,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15741,7 +15741,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15774,7 +15774,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15789,7 +15789,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -15807,7 +15807,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15873,7 +15873,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15939,7 +15939,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -15972,7 +15972,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16005,7 +16005,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16038,7 +16038,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16071,7 +16071,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16104,7 +16104,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16170,7 +16170,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16236,7 +16236,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16269,7 +16269,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16302,7 +16302,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16368,7 +16368,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16401,7 +16401,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -16434,7 +16434,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -16467,7 +16467,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>

--- a/docs/d/56/inyear.xlsx
+++ b/docs/d/56/inyear.xlsx
@@ -103,8 +103,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -883,7 +883,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -892,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="9" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -967,20 +967,20 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="M3" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -988,7 +988,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1012,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1068,20 +1068,20 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M4" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1089,7 +1089,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1097,8 +1097,8 @@
       <c r="P4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" s="9" t="n">
-        <v>0</v>
+      <c r="Q4" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R4" s="9" t="n">
         <v>0</v>
@@ -1173,20 +1173,20 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1194,7 +1194,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1278,20 +1278,20 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>69</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8</v>
+        <v>-11</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="M6" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1299,7 +1299,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1326,7 +1326,7 @@
         <v>4</v>
       </c>
       <c r="W6" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>7</v>
@@ -1383,20 +1383,20 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1404,7 +1404,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1425,7 +1425,7 @@
         <v>1</v>
       </c>
       <c r="U7" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V7" s="9" t="n">
         <v>1</v>
@@ -1488,20 +1488,20 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1509,7 +1509,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1593,20 +1593,20 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1698,20 +1698,20 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1719,7 +1719,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1799,20 +1799,20 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1820,7 +1820,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1829,7 +1829,7 @@
         <v>2</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>0</v>
@@ -1904,20 +1904,20 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1925,7 +1925,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2009,20 +2009,20 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2114,20 +2114,20 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -2135,7 +2135,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2215,20 +2215,20 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -2236,7 +2236,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2262,8 +2262,8 @@
       <c r="V15" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W15" s="9" t="n">
-        <v>1</v>
+      <c r="W15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>5</v>
@@ -2320,20 +2320,20 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -2341,7 +2341,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2365,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2421,20 +2421,20 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2522,20 +2522,20 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -2543,7 +2543,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2623,20 +2623,20 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2644,7 +2644,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2724,20 +2724,20 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -2745,7 +2745,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2825,20 +2825,20 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2846,7 +2846,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2930,20 +2930,20 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
+        <v>-18</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="M22" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2951,7 +2951,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3031,20 +3031,20 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -3052,7 +3052,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3079,7 +3079,7 @@
         <v>4</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>7</v>
@@ -3136,20 +3136,20 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M24" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3237,20 +3237,20 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="M25" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -3258,7 +3258,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3284,8 +3284,8 @@
       <c r="V25" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W25" s="9" t="n">
-        <v>2</v>
+      <c r="W25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>7</v>
@@ -3342,20 +3342,20 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M26" s="7" t="n">
+      <c r="M26" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -3363,7 +3363,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3447,20 +3447,20 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="M27" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -3468,7 +3468,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3477,7 +3477,7 @@
         <v>1</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
         <v>4</v>
       </c>
       <c r="W27" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>6</v>
@@ -3548,20 +3548,20 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3569,7 +3569,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3653,20 +3653,20 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="M29" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3674,7 +3674,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3758,20 +3758,20 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -3779,7 +3779,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O30" s="8" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3806,7 +3806,7 @@
         <v>4</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X30" s="10" t="n">
         <v>5</v>
@@ -3863,20 +3863,20 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M31" s="7" t="n">
+      <c r="M31" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3884,7 +3884,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O31" s="8" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3964,20 +3964,20 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="n">
+        <v>-21</v>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3985,7 +3985,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O32" s="8" t="inlineStr">
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4069,20 +4069,20 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M33" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -4090,7 +4090,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O33" s="8" t="inlineStr">
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4114,7 +4114,7 @@
         <v>1</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4174,20 +4174,20 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M34" s="7" t="n">
+      <c r="M34" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -4195,7 +4195,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O34" s="8" t="inlineStr">
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4275,20 +4275,20 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M35" s="7" t="n">
+      <c r="M35" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -4296,7 +4296,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O35" s="8" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4376,20 +4376,20 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M36" s="7" t="n">
+      <c r="M36" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -4397,7 +4397,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O36" s="8" t="inlineStr">
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4477,20 +4477,20 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M37" s="7" t="n">
+      <c r="M37" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -4498,7 +4498,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O37" s="8" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4578,20 +4578,20 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M38" s="7" t="n">
+      <c r="M38" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -4599,7 +4599,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O38" s="8" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4683,20 +4683,20 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -4704,7 +4704,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O39" s="8" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4730,8 +4730,8 @@
       <c r="V39" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W39" s="9" t="n">
-        <v>0</v>
+      <c r="W39" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>4</v>
@@ -4784,20 +4784,20 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M40" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -4805,7 +4805,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O40" s="8" t="inlineStr">
+      <c r="O40" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4829,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4889,20 +4889,20 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M41" s="7" t="n">
+      <c r="M41" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4910,7 +4910,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O41" s="8" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4994,20 +4994,20 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M42" s="7" t="n">
+      <c r="M42" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -5015,7 +5015,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O42" s="8" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5039,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5095,20 +5095,20 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M43" s="7" t="n">
+      <c r="M43" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -5116,7 +5116,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5200,20 +5200,20 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M44" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -5221,7 +5221,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O44" s="8" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5245,7 +5245,7 @@
         <v>1</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5313,12 +5313,12 @@
       <c r="K45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="8" t="inlineStr">
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M45" s="7" t="n">
+      <c r="M45" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -5326,7 +5326,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O45" s="8" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5406,20 +5406,20 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M46" s="7" t="n">
+      <c r="M46" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -5427,7 +5427,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O46" s="8" t="inlineStr">
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5451,7 +5451,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5507,20 +5507,20 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M47" s="7" t="n">
+      <c r="M47" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -5528,7 +5528,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O47" s="8" t="inlineStr">
+      <c r="O47" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5608,20 +5608,20 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>9</v>
+        <v>-4</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M48" s="7" t="n">
+      <c r="M48" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -5629,13 +5629,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O48" s="8" t="inlineStr">
+      <c r="O48" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="9" t="n">
         <v>0</v>
@@ -5644,7 +5644,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="10" t="n">
         <v>1</v>
@@ -5656,7 +5656,7 @@
         <v>4</v>
       </c>
       <c r="W48" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>7</v>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5713,20 +5713,20 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>9</v>
+        <v>-5</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M49" s="7" t="n">
+      <c r="M49" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -5734,7 +5734,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O49" s="8" t="inlineStr">
+      <c r="O49" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5751,8 +5751,8 @@
       <c r="S49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T49" s="9" t="n">
-        <v>0</v>
+      <c r="T49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U49" s="9" t="n">
         <v>0</v>
@@ -5761,7 +5761,7 @@
         <v>4</v>
       </c>
       <c r="W49" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X49" s="10" t="n">
         <v>7</v>
@@ -5818,20 +5818,20 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M50" s="7" t="n">
+      <c r="M50" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -5839,7 +5839,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O50" s="8" t="inlineStr">
+      <c r="O50" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5927,12 +5927,12 @@
       <c r="K51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L51" s="8" t="inlineStr">
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M51" s="7" t="n">
+      <c r="M51" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5940,7 +5940,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O51" s="8" t="inlineStr">
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6020,20 +6020,20 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M52" s="7" t="n">
+      <c r="M52" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -6041,7 +6041,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O52" s="8" t="inlineStr">
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6068,7 +6068,7 @@
         <v>4</v>
       </c>
       <c r="W52" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X52" s="10" t="n">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6133,12 +6133,12 @@
       <c r="K53" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L53" s="8" t="inlineStr">
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M53" s="7" t="n">
+      <c r="M53" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -6146,7 +6146,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O53" s="8" t="inlineStr">
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6169,8 +6169,8 @@
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>3</v>
+      <c r="V53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6226,20 +6226,20 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M54" s="7" t="n">
+      <c r="M54" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -6247,7 +6247,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O54" s="8" t="inlineStr">
+      <c r="O54" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6271,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -6327,20 +6327,20 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M55" s="7" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M55" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -6348,7 +6348,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O55" s="8" t="inlineStr">
+      <c r="O55" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6428,20 +6428,20 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L56" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M56" s="7" t="n">
+      <c r="M56" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -6449,7 +6449,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O56" s="8" t="inlineStr">
+      <c r="O56" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6529,20 +6529,20 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M57" s="7" t="n">
+      <c r="M57" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -6550,7 +6550,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O57" s="8" t="inlineStr">
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6634,34 +6634,34 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K58" s="4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M58" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O58" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P58" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M58" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N58" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O58" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P58" s="9" t="n">
-        <v>2</v>
       </c>
       <c r="Q58" s="9" t="n">
         <v>1</v>
@@ -6739,20 +6739,20 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M59" s="7" t="n">
+      <c r="M59" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -6760,7 +6760,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O59" s="8" t="inlineStr">
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6853,7 +6853,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M60" s="7" t="n">
+      <c r="M60" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -6861,7 +6861,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O60" s="8" t="inlineStr">
+      <c r="O60" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6941,20 +6941,20 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M61" s="7" t="n">
+      <c r="M61" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6962,7 +6962,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O61" s="8" t="inlineStr">
+      <c r="O61" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7046,20 +7046,20 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M62" s="7" t="n">
+      <c r="M62" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -7067,7 +7067,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O62" s="8" t="inlineStr">
+      <c r="O62" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7094,7 +7094,7 @@
         <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>7</v>
@@ -7151,20 +7151,20 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M63" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M63" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -7172,13 +7172,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O63" s="8" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7256,20 +7256,20 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M64" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M64" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -7277,7 +7277,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O64" s="8" t="inlineStr">
+      <c r="O64" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7300,8 +7300,8 @@
       <c r="U64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="9" t="n">
-        <v>0</v>
+      <c r="V64" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7357,20 +7357,20 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M65" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M65" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -7378,7 +7378,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O65" s="8" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7401,11 +7401,11 @@
       <c r="U65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="9" t="n">
-        <v>0</v>
+      <c r="V65" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W65" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X65" s="9" t="n">
         <v>1</v>
@@ -7458,20 +7458,20 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M66" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M66" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -7479,7 +7479,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O66" s="8" t="inlineStr">
+      <c r="O66" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7563,20 +7563,20 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="8" t="inlineStr">
+        <v>-9</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M67" s="7" t="n">
+      <c r="M67" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -7584,7 +7584,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O67" s="8" t="inlineStr">
+      <c r="O67" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7608,7 +7608,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7664,20 +7664,20 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M68" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M68" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -7685,7 +7685,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O68" s="8" t="inlineStr">
+      <c r="O68" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7769,20 +7769,20 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M69" s="7" t="n">
+      <c r="M69" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -7790,7 +7790,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O69" s="8" t="inlineStr">
+      <c r="O69" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7813,8 +7813,8 @@
       <c r="U69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="9" t="n">
-        <v>3</v>
+      <c r="V69" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7874,20 +7874,20 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M70" s="7" t="n">
+      <c r="M70" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -7895,7 +7895,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O70" s="8" t="inlineStr">
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7979,20 +7979,20 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L71" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M71" s="7" t="n">
+      <c r="M71" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -8000,7 +8000,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O71" s="8" t="inlineStr">
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8024,7 +8024,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -8080,20 +8080,20 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M72" s="7" t="n">
+      <c r="M72" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -8101,7 +8101,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O72" s="8" t="inlineStr">
+      <c r="O72" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8185,20 +8185,20 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M73" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M73" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -8206,7 +8206,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O73" s="8" t="inlineStr">
+      <c r="O73" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8229,8 +8229,8 @@
       <c r="U73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="9" t="n">
-        <v>3</v>
+      <c r="V73" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8286,20 +8286,20 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M74" s="7" t="n">
+      <c r="M74" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -8307,7 +8307,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O74" s="8" t="inlineStr">
+      <c r="O74" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8387,20 +8387,20 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M75" s="7" t="n">
+        <v>-38</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M75" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -8408,7 +8408,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O75" s="8" t="inlineStr">
+      <c r="O75" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8488,20 +8488,20 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M76" s="7" t="n">
+      <c r="M76" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -8509,7 +8509,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O76" s="8" t="inlineStr">
+      <c r="O76" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8589,20 +8589,20 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M77" s="7" t="n">
+      <c r="M77" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -8610,7 +8610,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O77" s="8" t="inlineStr">
+      <c r="O77" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8690,20 +8690,20 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M78" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M78" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
@@ -8711,7 +8711,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O78" s="8" t="inlineStr">
+      <c r="O78" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8795,20 +8795,20 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M79" s="7" t="n">
+      <c r="M79" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -8816,7 +8816,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O79" s="8" t="inlineStr">
+      <c r="O79" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8896,20 +8896,20 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M80" s="7" t="n">
+      <c r="M80" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -8917,7 +8917,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O80" s="8" t="inlineStr">
+      <c r="O80" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8941,7 +8941,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8997,20 +8997,20 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M81" s="7" t="n">
+      <c r="M81" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -9018,7 +9018,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O81" s="8" t="inlineStr">
+      <c r="O81" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9098,20 +9098,20 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M82" s="7" t="n">
+      <c r="M82" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
@@ -9119,7 +9119,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O82" s="8" t="inlineStr">
+      <c r="O82" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9203,20 +9203,20 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M83" s="7" t="n">
+      <c r="M83" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -9224,13 +9224,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O83" s="8" t="inlineStr">
+      <c r="O83" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83" s="9" t="n">
         <v>0</v>
@@ -9304,20 +9304,20 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M84" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M84" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
@@ -9325,7 +9325,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O84" s="8" t="inlineStr">
+      <c r="O84" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9349,7 +9349,7 @@
         <v>1</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9409,20 +9409,20 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M85" s="7" t="n">
+      <c r="M85" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -9430,7 +9430,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O85" s="8" t="inlineStr">
+      <c r="O85" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9454,7 +9454,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9510,20 +9510,20 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M86" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M86" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
@@ -9531,7 +9531,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O86" s="8" t="inlineStr">
+      <c r="O86" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9615,20 +9615,20 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M87" s="7" t="n">
+      <c r="M87" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -9636,7 +9636,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O87" s="8" t="inlineStr">
+      <c r="O87" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9660,7 +9660,7 @@
         <v>1</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9720,20 +9720,20 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M88" s="7" t="n">
+      <c r="M88" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
@@ -9741,7 +9741,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O88" s="8" t="inlineStr">
+      <c r="O88" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9825,20 +9825,20 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M89" s="7" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M89" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -9846,7 +9846,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O89" s="8" t="inlineStr">
+      <c r="O89" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9870,7 +9870,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9930,20 +9930,20 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L90" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M90" s="7" t="n">
+      <c r="M90" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -9951,7 +9951,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O90" s="8" t="inlineStr">
+      <c r="O90" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10031,20 +10031,20 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M91" s="7" t="n">
+      <c r="M91" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -10052,7 +10052,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O91" s="8" t="inlineStr">
+      <c r="O91" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10076,7 +10076,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -10132,20 +10132,20 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="8" t="inlineStr">
+        <v>-9</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M92" s="7" t="n">
+      <c r="M92" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -10153,7 +10153,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O92" s="8" t="inlineStr">
+      <c r="O92" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10177,7 +10177,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -10237,20 +10237,20 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M93" s="7" t="n">
+      <c r="M93" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -10258,7 +10258,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O93" s="8" t="inlineStr">
+      <c r="O93" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10282,7 +10282,7 @@
         <v>1</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -10342,20 +10342,20 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M94" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M94" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
@@ -10363,7 +10363,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O94" s="8" t="inlineStr">
+      <c r="O94" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10443,20 +10443,20 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M95" s="7" t="n">
+      <c r="M95" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -10464,7 +10464,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O95" s="8" t="inlineStr">
+      <c r="O95" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10544,20 +10544,20 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M96" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M96" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
@@ -10565,7 +10565,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O96" s="8" t="inlineStr">
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10649,20 +10649,20 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M97" s="7" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M97" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -10670,7 +10670,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O97" s="8" t="inlineStr">
+      <c r="O97" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10763,7 +10763,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M98" s="7" t="n">
+      <c r="M98" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
@@ -10771,7 +10771,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O98" s="8" t="inlineStr">
+      <c r="O98" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10794,11 +10794,11 @@
       <c r="U98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W98" s="9" t="n">
-        <v>0</v>
+      <c r="V98" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W98" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X98" s="9" t="n">
         <v>3</v>
@@ -10849,20 +10849,20 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M99" s="7" t="n">
+      <c r="M99" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -10870,7 +10870,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O99" s="8" t="inlineStr">
+      <c r="O99" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10894,7 +10894,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10948,52 +10948,52 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K100" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M100" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O100" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="L100" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M100" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N100" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O100" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -11047,20 +11047,20 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L101" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M101" s="7" t="n">
+      <c r="M101" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -11068,7 +11068,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O101" s="8" t="inlineStr">
+      <c r="O101" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11146,20 +11146,20 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="8" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M102" s="7" t="n">
+      <c r="M102" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
@@ -11167,7 +11167,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O102" s="8" t="inlineStr">
+      <c r="O102" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11253,12 +11253,12 @@
       <c r="K103" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L103" s="8" t="inlineStr">
+      <c r="L103" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M103" s="7" t="n">
+      <c r="M103" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -11266,7 +11266,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O103" s="8" t="inlineStr">
+      <c r="O103" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11346,20 +11346,20 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M104" s="7" t="n">
+      <c r="M104" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -11367,7 +11367,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O104" s="8" t="inlineStr">
+      <c r="O104" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11451,20 +11451,20 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M105" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M105" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N105" s="4" t="inlineStr">
@@ -11472,7 +11472,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O105" s="8" t="inlineStr">
+      <c r="O105" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11556,20 +11556,20 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M106" s="7" t="n">
+      <c r="M106" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N106" s="4" t="inlineStr">
@@ -11577,7 +11577,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O106" s="8" t="inlineStr">
+      <c r="O106" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11601,7 +11601,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11657,20 +11657,20 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L107" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M107" s="7" t="n">
+      <c r="M107" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N107" s="4" t="inlineStr">
@@ -11678,7 +11678,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O107" s="8" t="inlineStr">
+      <c r="O107" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11693,7 +11693,7 @@
         <v>0</v>
       </c>
       <c r="S107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T107" s="9" t="n">
         <v>0</v>
@@ -11758,20 +11758,20 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M108" s="7" t="n">
+      <c r="M108" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N108" s="4" t="inlineStr">
@@ -11779,7 +11779,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O108" s="8" t="inlineStr">
+      <c r="O108" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11803,7 +11803,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11859,20 +11859,20 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M109" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M109" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N109" s="4" t="inlineStr">
@@ -11880,7 +11880,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O109" s="8" t="inlineStr">
+      <c r="O109" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11960,20 +11960,20 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M110" s="7" t="n">
+      <c r="M110" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N110" s="4" t="inlineStr">
@@ -11981,7 +11981,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O110" s="8" t="inlineStr">
+      <c r="O110" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12065,20 +12065,20 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M111" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M111" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N111" s="4" t="inlineStr">
@@ -12086,7 +12086,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O111" s="8" t="inlineStr">
+      <c r="O111" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12110,7 +12110,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -12156,7 +12156,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12170,20 +12170,20 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L112" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M112" s="7" t="n">
+      <c r="M112" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N112" s="4" t="inlineStr">
@@ -12191,7 +12191,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O112" s="8" t="inlineStr">
+      <c r="O112" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12214,11 +12214,11 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>3</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>5</v>
@@ -12271,20 +12271,20 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M113" s="7" t="n">
+        <v>-17</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M113" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N113" s="4" t="inlineStr">
@@ -12292,7 +12292,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O113" s="8" t="inlineStr">
+      <c r="O113" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12372,20 +12372,20 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M114" s="7" t="n">
+      <c r="M114" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N114" s="4" t="inlineStr">
@@ -12393,7 +12393,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O114" s="8" t="inlineStr">
+      <c r="O114" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12473,20 +12473,20 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M115" s="7" t="n">
+      <c r="M115" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N115" s="4" t="inlineStr">
@@ -12494,7 +12494,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O115" s="8" t="inlineStr">
+      <c r="O115" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12574,20 +12574,20 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L116" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M116" s="7" t="n">
+      <c r="M116" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N116" s="4" t="inlineStr">
@@ -12595,7 +12595,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O116" s="8" t="inlineStr">
+      <c r="O116" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12675,20 +12675,20 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M117" s="7" t="n">
+      <c r="M117" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N117" s="4" t="inlineStr">
@@ -12696,7 +12696,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O117" s="8" t="inlineStr">
+      <c r="O117" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12720,7 +12720,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12780,20 +12780,20 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M118" s="7" t="n">
+      <c r="M118" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N118" s="4" t="inlineStr">
@@ -12801,7 +12801,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O118" s="8" t="inlineStr">
+      <c r="O118" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12885,20 +12885,20 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M119" s="7" t="n">
+      <c r="M119" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N119" s="4" t="inlineStr">
@@ -12906,7 +12906,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O119" s="8" t="inlineStr">
+      <c r="O119" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12986,20 +12986,20 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M120" s="7" t="n">
+      <c r="M120" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N120" s="4" t="inlineStr">
@@ -13007,7 +13007,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O120" s="8" t="inlineStr">
+      <c r="O120" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13031,7 +13031,7 @@
         <v>1</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -13087,20 +13087,20 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L121" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M121" s="7" t="n">
+      <c r="M121" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
@@ -13108,7 +13108,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O121" s="8" t="inlineStr">
+      <c r="O121" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13174,7 +13174,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13188,20 +13188,20 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M122" s="7" t="n">
+      <c r="M122" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N122" s="4" t="inlineStr">
@@ -13209,7 +13209,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O122" s="8" t="inlineStr">
+      <c r="O122" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13235,8 +13235,8 @@
       <c r="V122" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W122" s="9" t="n">
-        <v>1</v>
+      <c r="W122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X122" s="10" t="n">
         <v>5</v>
@@ -13289,20 +13289,20 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M123" s="7" t="n">
+      <c r="M123" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N123" s="4" t="inlineStr">
@@ -13310,7 +13310,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O123" s="8" t="inlineStr">
+      <c r="O123" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13390,20 +13390,20 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M124" s="7" t="n">
+      <c r="M124" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N124" s="4" t="inlineStr">
@@ -13411,7 +13411,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O124" s="8" t="inlineStr">
+      <c r="O124" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13491,20 +13491,20 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M125" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M125" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N125" s="4" t="inlineStr">
@@ -13512,7 +13512,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O125" s="8" t="inlineStr">
+      <c r="O125" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13536,7 +13536,7 @@
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -13596,20 +13596,20 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M126" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L126" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M126" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N126" s="4" t="inlineStr">
@@ -13617,7 +13617,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O126" s="8" t="inlineStr">
+      <c r="O126" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13626,7 +13626,7 @@
         <v>2</v>
       </c>
       <c r="Q126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
@@ -13641,7 +13641,7 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -13701,20 +13701,20 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M127" s="7" t="n">
+      <c r="M127" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N127" s="4" t="inlineStr">
@@ -13722,7 +13722,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O127" s="8" t="inlineStr">
+      <c r="O127" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13806,20 +13806,20 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L128" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L128" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M128" s="7" t="n">
+      <c r="M128" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N128" s="4" t="inlineStr">
@@ -13827,7 +13827,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O128" s="8" t="inlineStr">
+      <c r="O128" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13915,12 +13915,12 @@
       <c r="K129" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L129" s="8" t="inlineStr">
+      <c r="L129" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M129" s="7" t="n">
+      <c r="M129" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N129" s="4" t="inlineStr">
@@ -13928,13 +13928,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O129" s="8" t="inlineStr">
+      <c r="O129" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q129" s="9" t="n">
         <v>0</v>
@@ -14008,20 +14008,20 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M130" s="7" t="n">
+      <c r="M130" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N130" s="4" t="inlineStr">
@@ -14029,7 +14029,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O130" s="8" t="inlineStr">
+      <c r="O130" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14109,20 +14109,20 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L131" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L131" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M131" s="7" t="n">
+      <c r="M131" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N131" s="4" t="inlineStr">
@@ -14130,7 +14130,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O131" s="8" t="inlineStr">
+      <c r="O131" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14157,7 +14157,7 @@
         <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>5</v>
@@ -14196,7 +14196,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14210,20 +14210,20 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M132" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L132" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M132" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N132" s="4" t="inlineStr">
@@ -14231,7 +14231,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O132" s="8" t="inlineStr">
+      <c r="O132" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14245,8 +14245,8 @@
       <c r="R132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S132" s="9" t="n">
-        <v>1</v>
+      <c r="S132" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T132" s="10" t="n">
         <v>1</v>
@@ -14315,20 +14315,20 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L133" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M133" s="7" t="n">
+      <c r="M133" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N133" s="4" t="inlineStr">
@@ -14336,7 +14336,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O133" s="8" t="inlineStr">
+      <c r="O133" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14416,20 +14416,20 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M134" s="7" t="n">
+      <c r="M134" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N134" s="4" t="inlineStr">
@@ -14437,7 +14437,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O134" s="8" t="inlineStr">
+      <c r="O134" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14521,20 +14521,20 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L135" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M135" s="7" t="n">
+      <c r="M135" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N135" s="4" t="inlineStr">
@@ -14542,7 +14542,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O135" s="8" t="inlineStr">
+      <c r="O135" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14622,20 +14622,20 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M136" s="7" t="n">
+        <v>-35</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M136" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N136" s="4" t="inlineStr">
@@ -14643,7 +14643,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O136" s="8" t="inlineStr">
+      <c r="O136" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14723,20 +14723,20 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L137" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M137" s="7" t="n">
+      <c r="M137" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N137" s="4" t="inlineStr">
@@ -14744,7 +14744,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O137" s="8" t="inlineStr">
+      <c r="O137" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14828,20 +14828,20 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M138" s="7" t="n">
+      <c r="M138" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
@@ -14849,7 +14849,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O138" s="8" t="inlineStr">
+      <c r="O138" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14858,7 +14858,7 @@
         <v>0</v>
       </c>
       <c r="Q138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R138" s="9" t="n">
         <v>0</v>
@@ -14933,20 +14933,20 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M139" s="7" t="n">
+      <c r="M139" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N139" s="4" t="inlineStr">
@@ -14954,7 +14954,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O139" s="8" t="inlineStr">
+      <c r="O139" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14978,7 +14978,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -15034,20 +15034,20 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L140" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M140" s="7" t="n">
+      <c r="M140" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N140" s="4" t="inlineStr">
@@ -15055,7 +15055,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O140" s="8" t="inlineStr">
+      <c r="O140" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15139,20 +15139,20 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M141" s="7" t="n">
+      <c r="M141" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N141" s="4" t="inlineStr">
@@ -15160,7 +15160,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O141" s="8" t="inlineStr">
+      <c r="O141" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15187,7 +15187,7 @@
         <v>4</v>
       </c>
       <c r="W141" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X141" s="10" t="n">
         <v>6</v>
@@ -15244,20 +15244,20 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M142" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L142" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M142" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N142" s="4" t="inlineStr">
@@ -15265,7 +15265,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O142" s="8" t="inlineStr">
+      <c r="O142" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15357,12 +15357,12 @@
       <c r="K143" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L143" s="8" t="inlineStr">
+      <c r="L143" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M143" s="7" t="n">
+      <c r="M143" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N143" s="4" t="inlineStr">
@@ -15370,7 +15370,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O143" s="8" t="inlineStr">
+      <c r="O143" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15385,7 +15385,7 @@
         <v>0</v>
       </c>
       <c r="S143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T143" s="10" t="n">
         <v>1</v>
@@ -15394,7 +15394,7 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -15454,20 +15454,20 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M144" s="7" t="n">
+      <c r="M144" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N144" s="4" t="inlineStr">
@@ -15475,7 +15475,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O144" s="8" t="inlineStr">
+      <c r="O144" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15609,7 +15609,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -15624,7 +15624,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -15657,7 +15657,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -15675,7 +15675,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15690,7 +15690,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -15741,13 +15741,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -15789,7 +15789,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -15822,7 +15822,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15840,7 +15840,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15906,7 +15906,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -15939,7 +15939,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -15987,7 +15987,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -16005,7 +16005,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16020,7 +16020,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -16038,7 +16038,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16053,7 +16053,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -16071,7 +16071,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16086,7 +16086,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -16119,7 +16119,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -16152,7 +16152,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -16185,7 +16185,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -16218,7 +16218,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -16236,7 +16236,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16284,7 +16284,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -16302,7 +16302,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -16368,7 +16368,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16416,7 +16416,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -16434,7 +16434,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -16449,7 +16449,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -16482,7 +16482,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -16515,7 +16515,7 @@
         <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/56/inyear.xlsx
+++ b/docs/d/56/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/56/inyear.xlsx
+++ b/docs/d/56/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/56/inyear.xlsx
+++ b/docs/d/56/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/56/inyear.xlsx
+++ b/docs/d/56/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/56/inyear.xlsx
+++ b/docs/d/56/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -906,8 +906,8 @@
       <c r="U2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="9" t="n">
-        <v>3</v>
+      <c r="V2" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>69</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="P6" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="10" t="n">
         <v>2</v>
@@ -1326,7 +1326,7 @@
         <v>4</v>
       </c>
       <c r="W6" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>7</v>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="P9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q9" s="9" t="n">
         <v>0</v>
@@ -1698,13 +1698,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U12" s="9" t="n">
         <v>0</v>
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>4</v>
       </c>
       <c r="W15" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>5</v>
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2724,13 +2724,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -3031,13 +3031,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" s="10" t="n">
         <v>1</v>
@@ -3548,17 +3548,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M28" s="8" t="n">
@@ -4174,13 +4174,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4683,13 +4683,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -5608,13 +5608,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5650,13 +5650,13 @@
         <v>1</v>
       </c>
       <c r="U48" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V48" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W48" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>7</v>
@@ -5713,13 +5713,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>4</v>
       </c>
       <c r="W49" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X49" s="10" t="n">
         <v>7</v>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6020,13 +6020,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6067,8 +6067,8 @@
       <c r="V52" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W52" s="9" t="n">
-        <v>3</v>
+      <c r="W52" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X52" s="10" t="n">
         <v>7</v>
@@ -6634,13 +6634,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6941,13 +6941,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7087,8 +7087,8 @@
       <c r="T62" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U62" s="9" t="n">
-        <v>0</v>
+      <c r="U62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V62" s="10" t="n">
         <v>4</v>
@@ -7151,13 +7151,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7874,13 +7874,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>0</v>
       </c>
       <c r="Q70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" s="9" t="n">
         <v>0</v>
@@ -8185,13 +8185,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>4</v>
       </c>
       <c r="W73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X73" s="10" t="n">
         <v>5</v>
@@ -8589,13 +8589,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8690,13 +8690,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8896,13 +8896,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8997,13 +8997,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9098,13 +9098,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9510,17 +9510,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L86" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9650,8 +9650,8 @@
       <c r="R87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S87" s="9" t="n">
-        <v>1</v>
+      <c r="S87" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T87" s="10" t="n">
         <v>1</v>
@@ -10544,13 +10544,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10649,13 +10649,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11960,13 +11960,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>6</v>
@@ -12170,13 +12170,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>5</v>
@@ -12372,13 +12372,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -13087,13 +13087,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13188,13 +13188,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>4</v>
       </c>
       <c r="W122" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X122" s="10" t="n">
         <v>5</v>
@@ -13390,13 +13390,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -13491,17 +13491,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L125" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-8</v>
+      </c>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M125" s="8" t="n">
@@ -13536,7 +13536,7 @@
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -13701,13 +13701,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13743,10 +13743,10 @@
         <v>1</v>
       </c>
       <c r="U127" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -14210,13 +14210,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14416,13 +14416,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>1</v>
       </c>
       <c r="S134" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T134" s="10" t="n">
         <v>1</v>
@@ -14521,13 +14521,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14622,13 +14622,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-35</v>
+        <v>-18</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -15034,13 +15034,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -15675,7 +15675,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15789,7 +15789,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -15939,7 +15939,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16005,7 +16005,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16152,7 +16152,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -16170,7 +16170,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16416,7 +16416,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">

--- a/docs/d/56/inyear.xlsx
+++ b/docs/d/56/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 14 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC144"/>
+  <dimension ref="A1:AC145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1011,8 +1011,8 @@
       <c r="U3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="9" t="n">
-        <v>3</v>
+      <c r="V3" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1173,17 +1173,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M5" s="8" t="n">
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>69</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="P11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" s="9" t="n">
         <v>1</v>
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>0</v>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="9" t="n">
         <v>1</v>
@@ -2869,8 +2869,8 @@
       <c r="U21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="9" t="n">
-        <v>3</v>
+      <c r="V21" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -3031,13 +3031,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3177,8 +3177,8 @@
       <c r="T24" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U24" s="9" t="n">
-        <v>0</v>
+      <c r="U24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V24" s="9" t="n">
         <v>2</v>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>4</v>
       </c>
       <c r="W25" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>7</v>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3488,8 +3488,8 @@
       <c r="T27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U27" s="9" t="n">
-        <v>0</v>
+      <c r="U27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V27" s="10" t="n">
         <v>4</v>
@@ -4889,13 +4889,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>4</v>
       </c>
       <c r="W41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" s="10" t="n">
         <v>7</v>
@@ -5200,13 +5200,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5507,13 +5507,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5608,13 +5608,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5650,13 +5650,13 @@
         <v>1</v>
       </c>
       <c r="U48" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V48" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W48" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>7</v>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6058,8 +6058,8 @@
       <c r="S52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T52" s="9" t="n">
-        <v>0</v>
+      <c r="T52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U52" s="9" t="n">
         <v>0</v>
@@ -6670,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" s="10" t="n">
         <v>1</v>
@@ -7151,13 +7151,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9337,10 +9337,10 @@
         <v>2</v>
       </c>
       <c r="R84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="S84" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T84" s="10" t="n">
         <v>1</v>
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9510,13 +9510,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9548,8 +9548,8 @@
       <c r="S86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T86" s="9" t="n">
-        <v>0</v>
+      <c r="T86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
@@ -10522,11 +10522,11 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>4861572</v>
+        <v>28680909</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Mainland Toastmasters</t>
+          <t>Lubrizol Texas Toastmasters</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
@@ -10544,17 +10544,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L96" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M96" s="8" t="n">
@@ -10571,7 +10571,7 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="9" t="n">
         <v>0</v>
@@ -10589,13 +10589,13 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X96" s="10" t="n">
-        <v>7</v>
+      <c r="X96" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
@@ -10606,14 +10606,8 @@
       <c r="AA96" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB96" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC96" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB96" s="4" t="n"/>
+      <c r="AC96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -10627,11 +10621,11 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>28679836</v>
+        <v>4861572</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters of Bay City, TX</t>
+          <t>Mainland Toastmasters</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
@@ -10649,13 +10643,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10676,7 +10670,7 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" s="9" t="n">
         <v>0</v>
@@ -10694,13 +10688,13 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X97" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
@@ -10712,9 +10706,13 @@
         <v>1</v>
       </c>
       <c r="AB97" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC97" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC97" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -10724,95 +10722,97 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>28676746</v>
+        <v>28679836</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Bayou Toastmasters</t>
+          <t>Toastmasters of Bay City, TX</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J98" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K98" s="4" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M98" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O98" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA98" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB98" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F98" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G98" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="J98" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="K98" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M98" s="8" t="n">
-        <v>46387</v>
-      </c>
-      <c r="N98" s="4" t="inlineStr">
-        <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O98" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V98" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W98" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X98" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z98" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB98" s="4" t="n"/>
       <c r="AC98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
@@ -10827,15 +10827,15 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>8273</v>
+        <v>28676746</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Cenla Gift Of Gab Toastmasters Club</t>
+          <t>Bayou Toastmasters</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10849,17 +10849,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L99" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10893,20 +10893,20 @@
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W99" s="9" t="n">
-        <v>0</v>
+      <c r="V99" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W99" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X99" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="9" t="n">
         <v>0</v>
@@ -10926,15 +10926,15 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>2015</v>
+        <v>8273</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Golden Triangle Toastmasters Club – Club #2015</t>
+          <t>Cenla Gift Of Gab Toastmasters Club</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10948,13 +10948,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10962,11 +10962,11 @@
         </is>
       </c>
       <c r="M100" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O100" s="7" t="inlineStr">
@@ -10999,16 +10999,16 @@
         <v>0</v>
       </c>
       <c r="X100" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA100" s="10" t="n">
-        <v>1</v>
+      <c r="Z100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB100" s="4" t="n"/>
       <c r="AC100" s="4" t="inlineStr"/>
@@ -11025,15 +11025,15 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>1225</v>
+        <v>2015</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Lake Charles Toastmasters Club</t>
+          <t>Golden Triangle Toastmasters Club – Club #2015</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11047,13 +11047,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11061,11 +11061,11 @@
         </is>
       </c>
       <c r="M101" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O101" s="7" t="inlineStr">
@@ -11092,22 +11092,22 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X101" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB101" s="4" t="n"/>
       <c r="AC101" s="4" t="inlineStr"/>
@@ -11124,11 +11124,11 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>28676467</v>
+        <v>1225</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Westlake Toastmasters</t>
+          <t>Lake Charles Toastmasters Club</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -11146,13 +11146,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11191,13 +11191,13 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X102" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -11214,24 +11214,24 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>6422</v>
+        <v>28676467</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>All Star Club</t>
+          <t>Westlake Toastmasters</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11245,13 +11245,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11259,11 +11259,11 @@
         </is>
       </c>
       <c r="M103" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O103" s="7" t="inlineStr">
@@ -11272,7 +11272,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -11295,21 +11295,19 @@
       <c r="W103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X103" s="10" t="n">
-        <v>7</v>
+      <c r="X103" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA103" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB103" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="Z103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="4" t="n"/>
       <c r="AC103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
@@ -11324,15 +11322,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>609083</v>
+        <v>6422</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Determined To Master Speaking</t>
+          <t>All Star Club</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11346,17 +11344,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -11376,22 +11374,22 @@
         <v>1</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T104" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U104" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="T104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11409,13 +11407,9 @@
         <v>1</v>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC104" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -11429,15 +11423,15 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>1294652</v>
+        <v>609083</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Houston Galleria Project Management Toastmasters</t>
+          <t>Determined To Master Speaking</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11451,17 +11445,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L105" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M105" s="8" t="n">
@@ -11478,7 +11472,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>1</v>
@@ -11489,14 +11483,14 @@
       <c r="S105" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" s="9" t="n">
-        <v>0</v>
+      <c r="T105" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U105" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11514,11 +11508,11 @@
         <v>1</v>
       </c>
       <c r="AB105" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC105" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -11534,15 +11528,15 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>7740898</v>
+        <v>1294652</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>On the Fly Toastmasters</t>
+          <t>Houston Galleria Project Management Toastmasters</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11556,13 +11550,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11586,13 +11580,13 @@
         <v>0</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106" s="9" t="n">
         <v>0</v>
@@ -11606,22 +11600,26 @@
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X106" s="9" t="n">
-        <v>3</v>
+      <c r="X106" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC106" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -11635,15 +11633,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>8609</v>
+        <v>7740898</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>South Main Speakers Club</t>
+          <t>On the Fly Toastmasters</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11657,13 +11655,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11693,7 +11691,7 @@
         <v>0</v>
       </c>
       <c r="S107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T107" s="9" t="n">
         <v>0</v>
@@ -11707,14 +11705,14 @@
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X107" s="10" t="n">
-        <v>5</v>
+      <c r="X107" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="10" t="n">
-        <v>1</v>
+      <c r="Z107" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
@@ -11732,15 +11730,15 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>5769311</v>
+        <v>8609</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>A+ Toastmasters</t>
+          <t>South Main Speakers Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
@@ -11758,13 +11756,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11794,7 +11792,7 @@
         <v>0</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T108" s="9" t="n">
         <v>0</v>
@@ -11809,7 +11807,7 @@
         <v>0</v>
       </c>
       <c r="X108" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -11821,7 +11819,7 @@
         <v>1</v>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC108" s="4" t="inlineStr"/>
     </row>
@@ -11837,15 +11835,15 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>28679288</v>
+        <v>5769311</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>KW Metropolitan Houston</t>
+          <t>A+ Toastmasters</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11859,13 +11857,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11903,8 +11901,8 @@
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V109" s="10" t="n">
-        <v>4</v>
+      <c r="V109" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11922,7 +11920,7 @@
         <v>1</v>
       </c>
       <c r="AB109" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC109" s="4" t="inlineStr"/>
     </row>
@@ -11938,15 +11936,15 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>484</v>
+        <v>28679288</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Professionally Speaking Singles Toastmasters Club</t>
+          <t>KW Metropolitan Houston</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11960,17 +11958,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -11987,10 +11985,10 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q110" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
@@ -11998,8 +11996,8 @@
       <c r="S110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T110" s="10" t="n">
-        <v>1</v>
+      <c r="T110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U110" s="9" t="n">
         <v>0</v>
@@ -12008,10 +12006,10 @@
         <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X110" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
@@ -12023,13 +12021,9 @@
         <v>1</v>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC110" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -12043,15 +12037,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>8607</v>
+        <v>484</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Talking Bull Club</t>
+          <t>Professionally Speaking Singles Toastmasters Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12065,17 +12059,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L111" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12094,8 +12088,8 @@
       <c r="P111" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q111" s="9" t="n">
-        <v>0</v>
+      <c r="Q111" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
@@ -12109,14 +12103,14 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
+      <c r="V111" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W111" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W111" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="X111" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -12128,11 +12122,11 @@
         <v>1</v>
       </c>
       <c r="AB111" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC111" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -12148,11 +12142,11 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>3402</v>
+        <v>8607</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Uptown Club</t>
+          <t>Talking Bull Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
@@ -12170,13 +12164,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12197,10 +12191,10 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -12208,17 +12202,17 @@
       <c r="S112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T112" s="9" t="n">
-        <v>0</v>
+      <c r="T112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="10" t="n">
-        <v>4</v>
+      <c r="V112" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W112" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>5</v>
@@ -12233,9 +12227,13 @@
         <v>1</v>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC112" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12249,15 +12247,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>28679489</v>
+        <v>3402</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Voices of Success Toastmasters Club</t>
+          <t>Uptown Club</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12271,13 +12269,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-17</v>
+        <v>-1</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12301,7 +12299,7 @@
         <v>0</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -12315,14 +12313,14 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>0</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X113" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="X113" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -12334,7 +12332,7 @@
         <v>1</v>
       </c>
       <c r="AB113" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC113" s="4" t="inlineStr"/>
     </row>
@@ -12346,19 +12344,19 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>28678756</v>
+        <v>28679489</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Community Health Choice Toastmasters Club</t>
+          <t>Voices of Success Toastmasters Club</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12372,13 +12370,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-6</v>
+        <v>-17</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12428,14 +12426,14 @@
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC114" s="4" t="inlineStr"/>
     </row>
@@ -12451,15 +12449,15 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>744705</v>
+        <v>28678756</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Dance and Toast Masters Club</t>
+          <t>Community Health Choice Toastmasters Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12473,13 +12471,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12523,14 +12521,14 @@
       <c r="W115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X115" s="10" t="n">
-        <v>6</v>
+      <c r="X115" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="10" t="n">
-        <v>1</v>
+      <c r="Z115" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -12552,11 +12550,11 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>4641488</v>
+        <v>744705</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>McConnell Jones</t>
+          <t>Dance and Toast Masters Club</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
@@ -12574,10 +12572,10 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K116" s="4" t="n">
         <v>-2</v>
@@ -12601,43 +12599,43 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA116" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB116" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="Q116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V116" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z116" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA116" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB116" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="AC116" s="4" t="inlineStr"/>
     </row>
@@ -12653,15 +12651,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>4772213</v>
+        <v>4641488</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Sound of Greenway</t>
+          <t>McConnell Jones</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12675,17 +12673,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12702,7 +12700,7 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q117" s="9" t="n">
         <v>0</v>
@@ -12713,20 +12711,20 @@
       <c r="S117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T117" s="10" t="n">
-        <v>1</v>
+      <c r="T117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X117" s="10" t="n">
-        <v>4</v>
+      <c r="X117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12738,13 +12736,9 @@
         <v>1</v>
       </c>
       <c r="AB117" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC117" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -12758,15 +12752,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>6951688</v>
+        <v>4772213</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Timmons Talkers</t>
+          <t>Sound of Greenway</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12780,17 +12774,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L118" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12818,20 +12812,20 @@
       <c r="S118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T118" s="9" t="n">
-        <v>0</v>
+      <c r="T118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X118" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
@@ -12843,11 +12837,11 @@
         <v>1</v>
       </c>
       <c r="AB118" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC118" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -12859,19 +12853,19 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>3356718</v>
+        <v>6951688</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Houston Medical Center Toastmasters</t>
+          <t>Timmons Talkers</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12885,13 +12879,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12935,22 +12929,26 @@
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X119" s="9" t="n">
-        <v>3</v>
+      <c r="X119" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB119" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC119" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC119" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -12964,15 +12962,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>5698</v>
+        <v>3356718</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Medically Speaking Toastmasters Club</t>
+          <t>Houston Medical Center Toastmasters</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12986,13 +12984,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -13016,7 +13014,7 @@
         <v>0</v>
       </c>
       <c r="Q120" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R120" s="9" t="n">
         <v>0</v>
@@ -13024,32 +13022,32 @@
       <c r="S120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T120" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U120" s="10" t="n">
-        <v>1</v>
+      <c r="T120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X120" s="10" t="n">
-        <v>7</v>
+      <c r="X120" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="10" t="n">
-        <v>1</v>
+      <c r="Z120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AC120" s="4" t="inlineStr"/>
     </row>
@@ -13065,15 +13063,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>3897</v>
+        <v>5698</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Post Oak Toastmasters</t>
+          <t>Medically Speaking Toastmasters Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13087,13 +13085,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13117,7 +13115,7 @@
         <v>0</v>
       </c>
       <c r="Q121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -13125,11 +13123,11 @@
       <c r="S121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" s="9" t="n">
-        <v>0</v>
+      <c r="T121" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V121" s="9" t="n">
         <v>2</v>
@@ -13138,7 +13136,7 @@
         <v>0</v>
       </c>
       <c r="X121" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -13150,7 +13148,7 @@
         <v>1</v>
       </c>
       <c r="AB121" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC121" s="4" t="inlineStr"/>
     </row>
@@ -13166,15 +13164,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>4659373</v>
+        <v>3897</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Spirited Speech Masters</t>
+          <t>Post Oak Toastmasters</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13188,17 +13186,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="8" t="n">
@@ -13217,26 +13215,26 @@
       <c r="P122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" s="10" t="n">
+      <c r="Q122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V122" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W122" s="10" t="n">
-        <v>5</v>
+      <c r="W122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X122" s="10" t="n">
         <v>5</v>
@@ -13251,7 +13249,7 @@
         <v>1</v>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC122" s="4" t="inlineStr"/>
     </row>
@@ -13267,15 +13265,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>8411</v>
+        <v>4659373</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>T. rex Talkers</t>
+          <t>Spirited Speech Masters</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13289,17 +13287,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L123" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M123" s="8" t="n">
@@ -13318,8 +13316,8 @@
       <c r="P123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" s="9" t="n">
-        <v>0</v>
+      <c r="Q123" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
@@ -13333,11 +13331,11 @@
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" s="9" t="n">
-        <v>0</v>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W123" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X123" s="10" t="n">
         <v>5</v>
@@ -13352,27 +13350,27 @@
         <v>1</v>
       </c>
       <c r="AB123" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AC123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>3922610</v>
+        <v>8411</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>C &amp; F Leaders Club</t>
+          <t>T. rex Talkers</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
@@ -13390,13 +13388,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13435,13 +13433,13 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X124" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -13469,11 +13467,11 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>4815729</v>
+        <v>3922610</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Find Your Voice Toastmasters</t>
+          <t>C &amp; F Leaders Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
@@ -13491,17 +13489,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="8" t="n">
@@ -13518,31 +13516,31 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V125" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X125" s="9" t="n">
-        <v>3</v>
+      <c r="X125" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -13554,13 +13552,9 @@
         <v>1</v>
       </c>
       <c r="AB125" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC125" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -13574,15 +13568,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>7011533</v>
+        <v>4815729</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Mente Abierta</t>
+          <t>Find Your Voice Toastmasters</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13596,17 +13590,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K126" s="4" t="n">
         <v>-8</v>
       </c>
-      <c r="L126" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M126" s="8" t="n">
@@ -13631,11 +13625,11 @@
       <c r="R126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S126" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T126" s="10" t="n">
-        <v>1</v>
+      <c r="S126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U126" s="9" t="n">
         <v>0</v>
@@ -13646,8 +13640,8 @@
       <c r="W126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X126" s="10" t="n">
-        <v>4</v>
+      <c r="X126" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -13663,7 +13657,7 @@
       </c>
       <c r="AC126" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -13679,15 +13673,15 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>694851</v>
+        <v>7011533</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Pensadores de Houston Toastmasters Club</t>
+          <t>Mente Abierta</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13701,17 +13695,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M127" s="8" t="n">
@@ -13728,10 +13722,10 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13742,8 +13736,8 @@
       <c r="T127" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U127" s="10" t="n">
-        <v>5</v>
+      <c r="U127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
         <v>3</v>
@@ -13752,7 +13746,7 @@
         <v>0</v>
       </c>
       <c r="X127" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
@@ -13784,15 +13778,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>6043426</v>
+        <v>694851</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Pensadores Northwest</t>
+          <t>Pensadores de Houston Toastmasters Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13806,17 +13800,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L128" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M128" s="8" t="n">
@@ -13836,28 +13830,28 @@
         <v>0</v>
       </c>
       <c r="Q128" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" s="9" t="n">
-        <v>0</v>
+      <c r="S128" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U128" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X128" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
@@ -13869,9 +13863,13 @@
         <v>1</v>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC128" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC128" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -13881,15 +13879,15 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>1489448</v>
+        <v>6043426</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Big Red Toastmasters</t>
+          <t>Pensadores Northwest</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -13907,13 +13905,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13934,10 +13932,10 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R129" s="9" t="n">
         <v>0</v>
@@ -13952,13 +13950,13 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X129" s="9" t="n">
-        <v>1</v>
+      <c r="X129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -13970,7 +13968,7 @@
         <v>1</v>
       </c>
       <c r="AB129" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC129" s="4" t="inlineStr"/>
     </row>
@@ -13986,15 +13984,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>4911</v>
+        <v>1489448</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Chatter Champions Toastmasters</t>
+          <t>Big Red Toastmasters</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -14008,13 +14006,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -14035,7 +14033,7 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q130" s="9" t="n">
         <v>0</v>
@@ -14053,25 +14051,25 @@
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X130" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="9" t="n">
-        <v>0</v>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB130" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC130" s="4" t="inlineStr"/>
     </row>
@@ -14087,15 +14085,15 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>28676463</v>
+        <v>4911</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>POP Houston Toastmasters Club</t>
+          <t>Chatter Champions Toastmasters</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14109,13 +14107,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14153,20 +14151,20 @@
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="10" t="n">
-        <v>4</v>
+      <c r="V131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X131" s="10" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="X131" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="10" t="n">
-        <v>1</v>
+      <c r="Z131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -14188,15 +14186,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>5324194</v>
+        <v>28676463</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Southeast Houston Toastmasters</t>
+          <t>POP Houston Toastmasters Club</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14210,13 +14208,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14245,41 +14243,37 @@
       <c r="R132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S132" s="10" t="n">
+      <c r="S132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X132" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA132" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB132" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T132" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z132" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA132" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB132" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC132" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -14293,15 +14287,15 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>1171828</v>
+        <v>5324194</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Voice of Moses</t>
+          <t>Southeast Houston Toastmasters</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14315,13 +14309,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14345,7 +14339,7 @@
         <v>0</v>
       </c>
       <c r="Q133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -14353,14 +14347,14 @@
       <c r="S133" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T133" s="9" t="n">
-        <v>0</v>
+      <c r="T133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
@@ -14378,9 +14372,13 @@
         <v>1</v>
       </c>
       <c r="AB133" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC133" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC133" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -14390,19 +14388,19 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>5916</v>
+        <v>1171828</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Cy-Fair Super Speakers Club</t>
+          <t>Voice of Moses</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14416,17 +14414,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
@@ -14443,31 +14441,31 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R134" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S134" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T134" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U134" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V134" s="10" t="n">
-        <v>4</v>
+      <c r="T134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W134" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X134" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
@@ -14481,11 +14479,7 @@
       <c r="AB134" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AC134" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+      <c r="AC134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -14499,15 +14493,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>1774612</v>
+        <v>5916</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Cypress Toastmasters Club</t>
+          <t>Cy-Fair Super Speakers Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14521,17 +14515,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L135" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M135" s="8" t="n">
@@ -14548,31 +14542,31 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q135" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="S135" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T135" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U135" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="X135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -14584,9 +14578,13 @@
         <v>1</v>
       </c>
       <c r="AB135" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC135" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC135" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -14600,15 +14598,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>28679396</v>
+        <v>1774612</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Group 1 Automotive - BSC Toastmasters</t>
+          <t>Cypress Toastmasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14622,13 +14620,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-18</v>
+        <v>-3</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14649,7 +14647,7 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q136" s="9" t="n">
         <v>0</v>
@@ -14667,25 +14665,25 @@
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X136" s="10" t="n">
-        <v>6</v>
+      <c r="X136" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC136" s="4" t="inlineStr"/>
     </row>
@@ -14701,15 +14699,15 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>3116</v>
+        <v>28679396</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>JSC Toastmasters Club</t>
+          <t>Group 1 Automotive - BSC Toastmasters</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14723,13 +14721,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-5</v>
+        <v>-18</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14750,7 +14748,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -14768,31 +14766,27 @@
         <v>0</v>
       </c>
       <c r="V137" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X137" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="10" t="n">
-        <v>1</v>
+      <c r="Z137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB137" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC137" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -14806,15 +14800,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>4969</v>
+        <v>3116</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Talk of the Town Toastmasters</t>
+          <t>JSC Toastmasters Club</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14828,13 +14822,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14858,7 +14852,7 @@
         <v>0</v>
       </c>
       <c r="Q138" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R138" s="9" t="n">
         <v>0</v>
@@ -14866,20 +14860,20 @@
       <c r="S138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T138" s="10" t="n">
-        <v>1</v>
+      <c r="T138" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X138" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
@@ -14891,11 +14885,11 @@
         <v>1</v>
       </c>
       <c r="AB138" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC138" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -14911,15 +14905,15 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>28680594</v>
+        <v>4969</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Work Texas Toastmasters</t>
+          <t>Talk of the Town Toastmasters</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14933,17 +14927,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
@@ -14963,7 +14957,7 @@
         <v>0</v>
       </c>
       <c r="Q139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R139" s="9" t="n">
         <v>0</v>
@@ -14971,20 +14965,20 @@
       <c r="S139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T139" s="9" t="n">
-        <v>0</v>
+      <c r="T139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U139" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X139" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
@@ -14996,9 +14990,13 @@
         <v>1</v>
       </c>
       <c r="AB139" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC139" s="4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AC139" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -15008,15 +15006,15 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>4908</v>
+        <v>28680594</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Boeing Club</t>
+          <t>Work Texas Toastmasters</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
@@ -15034,17 +15032,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L140" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M140" s="8" t="n">
@@ -15072,38 +15070,34 @@
       <c r="S140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T140" s="10" t="n">
-        <v>1</v>
+      <c r="T140" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U140" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X140" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="9" t="n">
-        <v>0</v>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB140" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC140" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -15117,15 +15111,15 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>839</v>
+        <v>4908</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Daybreakers Toastmasters Club</t>
+          <t>Boeing Club</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15139,17 +15133,17 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L141" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M141" s="8" t="n">
@@ -15177,36 +15171,36 @@
       <c r="S141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T141" s="9" t="n">
-        <v>0</v>
+      <c r="T141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V141" s="10" t="n">
-        <v>4</v>
+      <c r="V141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W141" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X141" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="10" t="n">
-        <v>1</v>
+      <c r="Z141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB141" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC141" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -15222,15 +15216,15 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>28678020</v>
+        <v>839</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>ENGIE Toastmasters - Verbal Visionaries</t>
+          <t>Daybreakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15244,25 +15238,25 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L142" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M142" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O142" s="7" t="inlineStr">
@@ -15271,7 +15265,7 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q142" s="9" t="n">
         <v>0</v>
@@ -15292,10 +15286,10 @@
         <v>4</v>
       </c>
       <c r="W142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X142" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="X142" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
@@ -15303,15 +15297,15 @@
       <c r="Z142" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA142" s="9" t="n">
-        <v>0</v>
+      <c r="AA142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB142" s="4" t="n">
         <v>10</v>
       </c>
       <c r="AC142" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -15327,15 +15321,15 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>1295052</v>
+        <v>28678020</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Health Wealth and Happiness Toastmasters</t>
+          <t>ENGIE Toastmasters - Verbal Visionaries</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15352,10 +15346,10 @@
         <v>14</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15363,11 +15357,11 @@
         </is>
       </c>
       <c r="M143" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N143" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O143" s="7" t="inlineStr">
@@ -15376,7 +15370,7 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q143" s="9" t="n">
         <v>0</v>
@@ -15385,22 +15379,22 @@
         <v>0</v>
       </c>
       <c r="S143" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T143" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T143" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V143" s="9" t="n">
-        <v>2</v>
+      <c r="V143" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X143" s="10" t="n">
-        <v>6</v>
+      <c r="X143" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
@@ -15408,15 +15402,15 @@
       <c r="Z143" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA143" s="10" t="n">
-        <v>1</v>
+      <c r="AA143" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB143" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC143" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -15432,97 +15426,202 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
+        <v>1295052</v>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Health Wealth and Happiness Toastmasters</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G144" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J144" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K144" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M144" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O144" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P144" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T144" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA144" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB144" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC144" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="n">
         <v>5512862</v>
       </c>
-      <c r="D144" s="4" t="inlineStr">
+      <c r="D145" s="4" t="inlineStr">
         <is>
           <t>KW Memorial Toastmasters</t>
         </is>
       </c>
-      <c r="E144" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G144" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H144" s="4" t="inlineStr">
+      <c r="E145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G145" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
         <is>
           <t>Smedley</t>
         </is>
       </c>
-      <c r="I144" s="4" t="n">
+      <c r="I145" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="J144" s="4" t="n">
+      <c r="J145" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="K144" s="4" t="n">
+      <c r="K145" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="L144" s="7" t="inlineStr">
+      <c r="L145" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M144" s="8" t="n">
+      <c r="M145" s="8" t="n">
         <v>46387</v>
       </c>
-      <c r="N144" s="4" t="inlineStr">
+      <c r="N145" s="4" t="inlineStr">
         <is>
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O144" s="7" t="inlineStr">
+      <c r="O145" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB144" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC144" s="4" t="inlineStr"/>
+      <c r="P145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB145" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC145" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC144"/>
+  <autoFilter ref="A1:AC145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15609,7 +15708,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -15624,7 +15723,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -15708,7 +15807,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15741,7 +15840,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -15774,13 +15873,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -15939,7 +16038,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16137,13 +16236,13 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -16200,16 +16299,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -16218,7 +16317,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
